--- a/tame_output/ON/bt/strategyON_20240424.xlsx
+++ b/tame_output/ON/bt/strategyON_20240424.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-579.9%</t>
+          <t>-579.7%</t>
         </is>
       </c>
     </row>
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705546</v>
+        <v>3.311607601705545</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045694</v>
+        <v>3.317575502045693</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078594</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240574</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085276</v>
+        <v>3.685157806085277</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282097</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116211</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081562</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425322</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702406</v>
+        <v>3.747699084702408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906222</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781943</v>
+        <v>3.784680945781945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567239</v>
+        <v>3.800825778567241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487768</v>
+        <v>3.78930753648777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309721</v>
+        <v>3.833249172309722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858724</v>
+        <v>3.839370871858725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096469</v>
+        <v>3.85615817609647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761804</v>
+        <v>3.787326853761805</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255781</v>
+        <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860422</v>
+        <v>3.763178672860424</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575948</v>
+        <v>3.78471521857595</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430982</v>
+        <v>3.753878996430984</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077639</v>
+        <v>3.692928280077641</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457896</v>
+        <v>3.770419008457898</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180805</v>
+        <v>3.760330111180806</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879198</v>
+        <v>3.723562653879199</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568102</v>
+        <v>3.729966140568103</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963413</v>
+        <v>3.782918957963414</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192811</v>
+        <v>3.828547911192812</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966253</v>
+        <v>3.845043810966252</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
@@ -46240,10 +46240,10 @@
         <v>2.764596792240779</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.18315032999205</v>
+        <v>-4.181414760575667</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.090980235930211</v>
+        <v>1.091674463696765</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.7041038773607566</v>

--- a/tame_output/ON/bt/strategyON_20240424.xlsx
+++ b/tame_output/ON/bt/strategyON_20240424.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>53.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-30.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-35.2%</t>
+          <t>-44.6%</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.3%</t>
+          <t>-75.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-579.7%</t>
+          <t>-579.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-34.5%</t>
+          <t>-45.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-267.1%</t>
+          <t>-276.6%</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-167.2%</t>
+          <t>-167.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-211.8%</t>
+          <t>-221.3%</t>
         </is>
       </c>
     </row>
@@ -45340,19 +45340,19 @@
         <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.152965457527332</v>
+        <v>3.058237476829494</v>
       </c>
       <c r="D1904" t="n">
         <v>-8.964806701605866</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4333136474287613</v>
+        <v>-0.5280416281265996</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.677622451149987</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.546391986837341</v>
+        <v>1.451664006139503</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.763178672860424</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.14833294427436</v>
+        <v>3.053604963576521</v>
       </c>
       <c r="D1905" t="n">
         <v>-8.832531227974979</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3850359712293794</v>
+        <v>-0.4797639519272177</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.5453469775191</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.6211247577629</v>
+        <v>1.526396777065061</v>
       </c>
     </row>
     <row r="1906">
@@ -45386,19 +45386,19 @@
         <v>3.78471521857595</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.151148004961996</v>
+        <v>3.056420024264158</v>
       </c>
       <c r="D1906" t="n">
         <v>-8.641931553301825</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3059810406724814</v>
+        <v>-0.4007090213703197</v>
       </c>
       <c r="F1906" t="n">
         <v>-2.354747302845948</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.738299623254428</v>
+        <v>1.64357164255659</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753878996430984</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.164054346185655</v>
+        <v>3.069326365487817</v>
       </c>
       <c r="D1907" t="n">
         <v>-8.392931754618244</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1934747799753902</v>
+        <v>-0.2882027606732285</v>
       </c>
       <c r="F1907" t="n">
         <v>-2.354747302845948</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.751205964478087</v>
+        <v>1.656477983780248</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692928280077641</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.036078416586436</v>
+        <v>2.941350435888598</v>
       </c>
       <c r="D1908" t="n">
         <v>-8.498521744391349</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3636867054838504</v>
+        <v>-0.4584146861816887</v>
       </c>
       <c r="F1908" t="n">
         <v>-2.460337292619052</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.559876041015005</v>
+        <v>1.465148060317167</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770419008457898</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.084622758463523</v>
+        <v>2.989894777765684</v>
       </c>
       <c r="D1909" t="n">
         <v>-8.517256646509946</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3226363244542032</v>
+        <v>-0.4173643051520415</v>
       </c>
       <c r="F1909" t="n">
         <v>-2.460337292619052</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.608420382892092</v>
+        <v>1.513692402194253</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.760330111180806</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.964743835775355</v>
+        <v>2.870015855077517</v>
       </c>
       <c r="D1910" t="n">
         <v>-8.369316605102346</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.3833392305793311</v>
+        <v>-0.4780672112771693</v>
       </c>
       <c r="F1910" t="n">
         <v>-2.440016376710494</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.500734009749059</v>
+        <v>1.40600602905122</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723562653879199</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.956029849521877</v>
+        <v>2.861301868824039</v>
       </c>
       <c r="D1911" t="n">
         <v>-8.242424198667276</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.341296254258781</v>
+        <v>-0.4360242349566192</v>
       </c>
       <c r="F1911" t="n">
         <v>-2.313123970275424</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.568155467356622</v>
+        <v>1.473427486658784</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.729966140568103</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.949069237426784</v>
+        <v>2.854341256728945</v>
       </c>
       <c r="D1912" t="n">
         <v>-8.198875791896585</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3308375036455975</v>
+        <v>-0.4255654843434358</v>
       </c>
       <c r="F1912" t="n">
         <v>-2.313123970275424</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.561194855261529</v>
+        <v>1.466466874563691</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782918957963414</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.963531591807927</v>
+        <v>2.868803611110089</v>
       </c>
       <c r="D1913" t="n">
         <v>-7.956727398442727</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2195157918829111</v>
+        <v>-0.3142437725807494</v>
       </c>
       <c r="F1913" t="n">
         <v>-2.313123970275424</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.575657209642672</v>
+        <v>1.480929228944834</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828547911192812</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.958063712267122</v>
+        <v>2.863335731569284</v>
       </c>
       <c r="D1914" t="n">
         <v>-7.893498026674378</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1996919227163767</v>
+        <v>-0.294419903414215</v>
       </c>
       <c r="F1914" t="n">
         <v>-2.313123970275424</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.570189330101867</v>
+        <v>1.475461349404029</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828049353262042</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.955561806277699</v>
+        <v>2.86083382557986</v>
       </c>
       <c r="D1915" t="n">
         <v>-7.707010334297372</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1275987517549977</v>
+        <v>-0.222326732452836</v>
       </c>
       <c r="F1915" t="n">
         <v>-2.126636277898418</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.679580039538648</v>
+        <v>1.58485205884081</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812450103389904</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.963262784515024</v>
+        <v>2.868534803817186</v>
       </c>
       <c r="D1916" t="n">
         <v>-7.685861135393929</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1114380939562949</v>
+        <v>-0.2061660746541332</v>
       </c>
       <c r="F1916" t="n">
         <v>-2.105487078994975</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.699970537118039</v>
+        <v>1.605242556420201</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748324832788088</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.959043492862075</v>
+        <v>2.864315512164236</v>
       </c>
       <c r="D1917" t="n">
         <v>-7.442095693410485</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.01815120881586685</v>
+        <v>-0.1128791895137051</v>
       </c>
       <c r="F1917" t="n">
         <v>-2.105487078994975</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.69575124546509</v>
+        <v>1.601023264767252</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824307657527521</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.961167806782091</v>
+        <v>2.866439826084252</v>
       </c>
       <c r="D1918" t="n">
         <v>-7.178067626217224</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.08958433198145332</v>
+        <v>-0.005143648716384952</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.903621680179021</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.818994798674678</v>
+        <v>1.72426681797684</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826351398749178</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.953909881765793</v>
+        <v>2.859181901067954</v>
       </c>
       <c r="D1919" t="n">
         <v>-6.92821723226815</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1822665645447854</v>
+        <v>0.08753858384694713</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.903621680179021</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.81173687365838</v>
+        <v>1.717008892960542</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835954411481492</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.957509005286441</v>
+        <v>2.862781024588603</v>
       </c>
       <c r="D1920" t="n">
         <v>-6.624649743264171</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3072926836670256</v>
+        <v>0.2125647029691873</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.903621680179021</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.815335997179029</v>
+        <v>1.720608016481191</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780930335862981</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.970836511340995</v>
+        <v>2.876108530643157</v>
       </c>
       <c r="D1921" t="n">
         <v>-6.551169834412157</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.350012153262385</v>
+        <v>0.2552841725645467</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.830141771327007</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.872751448544791</v>
+        <v>1.778023467846953</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773761647102775</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.969856988957292</v>
+        <v>2.875129008259454</v>
       </c>
       <c r="D1922" t="n">
         <v>-6.326136834743334</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4390458307462111</v>
+        <v>0.3443178500483728</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.605108771658184</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.006791725962382</v>
+        <v>1.912063745264544</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764614304353067</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.974551790011609</v>
+        <v>2.879823809313771</v>
       </c>
       <c r="D1923" t="n">
         <v>-6.111502457106927</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5295943828550911</v>
+        <v>0.4348664021572528</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.390474394021777</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.140267153598543</v>
+        <v>2.045539172900705</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.798811195544776</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.955746048795405</v>
+        <v>2.861018068097567</v>
       </c>
       <c r="D1924" t="n">
         <v>-5.844902100132575</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6174287844286277</v>
+        <v>0.5227008037307894</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.390474394021777</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.121461412382339</v>
+        <v>2.026733431684501</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797691308712288</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.957489125420282</v>
+        <v>2.862761144722444</v>
       </c>
       <c r="D1925" t="n">
         <v>-5.604471603327715</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.715344059775449</v>
+        <v>0.6206160790776107</v>
       </c>
       <c r="F1925" t="n">
         <v>-1.150043897216917</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.267462787090133</v>
+        <v>2.172734806392294</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.821589933837679</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.961418439255103</v>
+        <v>2.866690458557264</v>
       </c>
       <c r="D1926" t="n">
         <v>-5.36168079567827</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8163896966700475</v>
+        <v>0.7216617159722092</v>
       </c>
       <c r="F1926" t="n">
         <v>-1.150043897216917</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.271392100924953</v>
+        <v>2.176664120227115</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.82232342234996</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.962097023172443</v>
+        <v>2.867369042474604</v>
       </c>
       <c r="D1927" t="n">
         <v>-5.245740946053084</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8634442204374615</v>
+        <v>0.7687162397396232</v>
       </c>
       <c r="F1927" t="n">
         <v>-1.073222166200793</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.318163723451967</v>
+        <v>2.223435742754129</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.848613050972333</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.959095094392436</v>
+        <v>2.864367113694598</v>
       </c>
       <c r="D1928" t="n">
         <v>-5.003085357629921</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9575045270267206</v>
+        <v>0.8627765463288823</v>
       </c>
       <c r="F1928" t="n">
         <v>-1.073222166200793</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.31516179467196</v>
+        <v>2.220433813974122</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818665376145932</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.96067413140305</v>
+        <v>2.865946150705212</v>
       </c>
       <c r="D1929" t="n">
         <v>-4.78306455959291</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.047091883252139</v>
+        <v>0.9523639025543007</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.9320023211328128</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.401472738723363</v>
+        <v>2.306744758025525</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.843270952009944</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.976568314204874</v>
+        <v>2.881840333507035</v>
       </c>
       <c r="D1930" t="n">
         <v>-4.583815929688101</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.142685518015886</v>
+        <v>1.047957537318048</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.9320023211328128</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.417366921525186</v>
+        <v>2.322638940827348</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845043810966252</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.977714158645175</v>
+        <v>2.882986177947337</v>
       </c>
       <c r="D1931" t="n">
         <v>-4.424300826168731</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.207637403863936</v>
+        <v>1.112909423166097</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.7724872176134429</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.51422182807711</v>
+        <v>2.419493847379272</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791269976046989</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.987802261206615</v>
+        <v>2.893074280508777</v>
       </c>
       <c r="D1932" t="n">
         <v>-4.279628681068994</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.275594364465271</v>
+        <v>1.180866383767432</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.6278150725137055</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.611113217698392</v>
+        <v>2.516385237000554</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735835647412096</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.903141953293337</v>
+        <v>2.808413972595499</v>
       </c>
       <c r="D1933" t="n">
         <v>-4.261859222138038</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.198041840124374</v>
+        <v>1.103313859426536</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.6100456135827499</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.537114585143687</v>
+        <v>2.442386604445849</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762643902144509</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.925542446615903</v>
+        <v>2.830814465918065</v>
       </c>
       <c r="D1934" t="n">
         <v>-4.175059724359029</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.255162132558544</v>
+        <v>1.160434151860706</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.6100456135827499</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.559515078466253</v>
+        <v>2.464787097768415</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729142822900688</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.925614847989315</v>
+        <v>2.830886867291477</v>
       </c>
       <c r="D1935" t="n">
         <v>-4.075367109630017</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.295111579823561</v>
+        <v>1.200383599125723</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.5103529988537381</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.619403048677072</v>
+        <v>2.524675067979234</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743216620473594</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.936621770464017</v>
+        <v>2.841893789766179</v>
       </c>
       <c r="D1936" t="n">
         <v>-4.143737295954027</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.278770427768659</v>
+        <v>1.184042447070821</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.5010772998175231</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.635975390573503</v>
+        <v>2.541247409875665</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714175563978363</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.927058479095908</v>
+        <v>2.83233049839807</v>
       </c>
       <c r="D1937" t="n">
         <v>-4.022320866327551</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.317773708251141</v>
+        <v>1.223045727553303</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.5010772998175231</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.626412099205395</v>
+        <v>2.531684118507556</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710903155887697</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.751768044136295</v>
+        <v>2.657040063438457</v>
       </c>
       <c r="D1938" t="n">
         <v>-4.053314025656256</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.130086009560046</v>
+        <v>1.035358028862207</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.5010772998175231</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.451121664245782</v>
+        <v>2.356393683547943</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746038950675894</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.756335276128083</v>
+        <v>2.661607295430245</v>
       </c>
       <c r="D1939" t="n">
         <v>-3.877839765863787</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.204842945468821</v>
+        <v>1.110114964770983</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.5010772998175231</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.455688896237569</v>
+        <v>2.360960915539731</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.76502074769544</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.756346750014881</v>
+        <v>2.661618769317042</v>
       </c>
       <c r="D1940" t="n">
         <v>-3.988776018505035</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.160479918299119</v>
+        <v>1.065751937601281</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.5010772998175231</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.455700370124367</v>
+        <v>2.360972389426529</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773206721581285</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.759478135234786</v>
+        <v>2.664750154536948</v>
       </c>
       <c r="D1941" t="n">
         <v>-4.191802596048269</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.082400672501731</v>
+        <v>0.9876726918038932</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.7041038773607566</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.337015808818332</v>
+        <v>2.242287828120494</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784340376734155</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.769650521666918</v>
+        <v>2.67492254096908</v>
       </c>
       <c r="D1942" t="n">
         <v>-4.033876997112976</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.155743298507981</v>
+        <v>1.061015317810143</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.7041038773607566</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.347188195250465</v>
+        <v>2.252460214552626</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.858908439567291</v>
+        <v>3.812548696413794</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.764596792240779</v>
+        <v>2.669868811542941</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.181414760575667</v>
+        <v>-4.182198250924104</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.091674463696765</v>
+        <v>0.9966330868595517</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.7041038773607566</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.342134465824325</v>
+        <v>2.247406485126487</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240424.xlsx
+++ b/tame_output/ON/bt/strategyON_20240424.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>57.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,22 +786,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,31 +815,31 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-30.3%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-44.6%</t>
+          <t>-15.8%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.3%</t>
+          <t>-78.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.3%</t>
+          <t>116.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,11 +931,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.8%</t>
+          <t>135.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.3%</t>
+          <t>95.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-74.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>96.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-579.8%</t>
+          <t>-564.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,16 +1084,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-45.6%</t>
+          <t>-34.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-276.6%</t>
+          <t>-261.0%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-167.4%</t>
+          <t>-167.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-221.3%</t>
+          <t>-150.9%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1943"/>
+  <dimension ref="A1:G1944"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45340,19 +45340,19 @@
         <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.058237476829494</v>
+        <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
         <v>-8.964806701605866</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5280416281265996</v>
+        <v>-0.4333136474287613</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.677622451149987</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.451664006139503</v>
+        <v>1.546391986837341</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.763178672860424</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.053604963576521</v>
+        <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
         <v>-8.832531227974979</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4797639519272177</v>
+        <v>-0.3850359712293794</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.5453469775191</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.526396777065061</v>
+        <v>1.6211247577629</v>
       </c>
     </row>
     <row r="1906">
@@ -45386,19 +45386,19 @@
         <v>3.78471521857595</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.056420024264158</v>
+        <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
         <v>-8.641931553301825</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4007090213703197</v>
+        <v>-0.3059810406724814</v>
       </c>
       <c r="F1906" t="n">
         <v>-2.354747302845948</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.64357164255659</v>
+        <v>1.738299623254428</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753878996430984</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.069326365487817</v>
+        <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
         <v>-8.392931754618244</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2882027606732285</v>
+        <v>-0.1934747799753902</v>
       </c>
       <c r="F1907" t="n">
         <v>-2.354747302845948</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.656477983780248</v>
+        <v>1.751205964478087</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692928280077641</v>
       </c>
       <c r="C1908" t="n">
-        <v>2.941350435888598</v>
+        <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
         <v>-8.498521744391349</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4584146861816887</v>
+        <v>-0.3636867054838504</v>
       </c>
       <c r="F1908" t="n">
         <v>-2.460337292619052</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.465148060317167</v>
+        <v>1.559876041015005</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770419008457898</v>
       </c>
       <c r="C1909" t="n">
-        <v>2.989894777765684</v>
+        <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
         <v>-8.517256646509946</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4173643051520415</v>
+        <v>-0.3226363244542032</v>
       </c>
       <c r="F1909" t="n">
         <v>-2.460337292619052</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.513692402194253</v>
+        <v>1.608420382892092</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.760330111180806</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.870015855077517</v>
+        <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
         <v>-8.369316605102346</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4780672112771693</v>
+        <v>-0.3833392305793311</v>
       </c>
       <c r="F1910" t="n">
         <v>-2.440016376710494</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.40600602905122</v>
+        <v>1.500734009749059</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723562653879199</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.861301868824039</v>
+        <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
         <v>-8.242424198667276</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4360242349566192</v>
+        <v>-0.341296254258781</v>
       </c>
       <c r="F1911" t="n">
         <v>-2.313123970275424</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.473427486658784</v>
+        <v>1.568155467356622</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.729966140568103</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.854341256728945</v>
+        <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
         <v>-8.198875791896585</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4255654843434358</v>
+        <v>-0.3308375036455975</v>
       </c>
       <c r="F1912" t="n">
         <v>-2.313123970275424</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.466466874563691</v>
+        <v>1.561194855261529</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782918957963414</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.868803611110089</v>
+        <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
         <v>-7.956727398442727</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3142437725807494</v>
+        <v>-0.2195157918829111</v>
       </c>
       <c r="F1913" t="n">
         <v>-2.313123970275424</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.480929228944834</v>
+        <v>1.575657209642672</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828547911192812</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.863335731569284</v>
+        <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
         <v>-7.893498026674378</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.294419903414215</v>
+        <v>-0.1996919227163767</v>
       </c>
       <c r="F1914" t="n">
         <v>-2.313123970275424</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.475461349404029</v>
+        <v>1.570189330101867</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828049353262042</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.86083382557986</v>
+        <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
         <v>-7.707010334297372</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.222326732452836</v>
+        <v>-0.1275987517549977</v>
       </c>
       <c r="F1915" t="n">
         <v>-2.126636277898418</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.58485205884081</v>
+        <v>1.679580039538648</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812450103389904</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.868534803817186</v>
+        <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
         <v>-7.685861135393929</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2061660746541332</v>
+        <v>-0.1114380939562949</v>
       </c>
       <c r="F1916" t="n">
         <v>-2.105487078994975</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.605242556420201</v>
+        <v>1.699970537118039</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748324832788088</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.864315512164236</v>
+        <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
         <v>-7.442095693410485</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1128791895137051</v>
+        <v>-0.01815120881586685</v>
       </c>
       <c r="F1917" t="n">
         <v>-2.105487078994975</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.601023264767252</v>
+        <v>1.69575124546509</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824307657527521</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.866439826084252</v>
+        <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
         <v>-7.178067626217224</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.005143648716384952</v>
+        <v>0.08958433198145332</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.903621680179021</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.72426681797684</v>
+        <v>1.818994798674678</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826351398749178</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.859181901067954</v>
+        <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
         <v>-6.92821723226815</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.08753858384694713</v>
+        <v>0.1822665645447854</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.903621680179021</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.717008892960542</v>
+        <v>1.81173687365838</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835954411481492</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.862781024588603</v>
+        <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
         <v>-6.624649743264171</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2125647029691873</v>
+        <v>0.3072926836670256</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.903621680179021</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.720608016481191</v>
+        <v>1.815335997179029</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780930335862981</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.876108530643157</v>
+        <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
         <v>-6.551169834412157</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2552841725645467</v>
+        <v>0.350012153262385</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.830141771327007</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.778023467846953</v>
+        <v>1.872751448544791</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773761647102775</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.875129008259454</v>
+        <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
         <v>-6.326136834743334</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3443178500483728</v>
+        <v>0.4390458307462111</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.605108771658184</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.912063745264544</v>
+        <v>2.006791725962382</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764614304353067</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.879823809313771</v>
+        <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
         <v>-6.111502457106927</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4348664021572528</v>
+        <v>0.5295943828550911</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.390474394021777</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.045539172900705</v>
+        <v>2.140267153598543</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.798811195544776</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.861018068097567</v>
+        <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
         <v>-5.844902100132575</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5227008037307894</v>
+        <v>0.6174287844286277</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.390474394021777</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.026733431684501</v>
+        <v>2.121461412382339</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797691308712288</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.862761144722444</v>
+        <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
         <v>-5.604471603327715</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6206160790776107</v>
+        <v>0.715344059775449</v>
       </c>
       <c r="F1925" t="n">
         <v>-1.150043897216917</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.172734806392294</v>
+        <v>2.267462787090133</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.821589933837679</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.866690458557264</v>
+        <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
         <v>-5.36168079567827</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7216617159722092</v>
+        <v>0.8163896966700475</v>
       </c>
       <c r="F1926" t="n">
         <v>-1.150043897216917</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.176664120227115</v>
+        <v>2.271392100924953</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.82232342234996</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.867369042474604</v>
+        <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
         <v>-5.245740946053084</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7687162397396232</v>
+        <v>0.8634442204374615</v>
       </c>
       <c r="F1927" t="n">
         <v>-1.073222166200793</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.223435742754129</v>
+        <v>2.318163723451967</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.848613050972333</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.864367113694598</v>
+        <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
         <v>-5.003085357629921</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8627765463288823</v>
+        <v>0.9575045270267206</v>
       </c>
       <c r="F1928" t="n">
         <v>-1.073222166200793</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.220433813974122</v>
+        <v>2.31516179467196</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818665376145932</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.865946150705212</v>
+        <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
         <v>-4.78306455959291</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9523639025543007</v>
+        <v>1.047091883252139</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.9320023211328128</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.306744758025525</v>
+        <v>2.401472738723363</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.843270952009944</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.881840333507035</v>
+        <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
         <v>-4.583815929688101</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.047957537318048</v>
+        <v>1.142685518015886</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.9320023211328128</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.322638940827348</v>
+        <v>2.417366921525186</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845043810966252</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.882986177947337</v>
+        <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
         <v>-4.424300826168731</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.112909423166097</v>
+        <v>1.207637403863936</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.7724872176134429</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.419493847379272</v>
+        <v>2.51422182807711</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791269976046989</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.893074280508777</v>
+        <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
         <v>-4.279628681068994</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.180866383767432</v>
+        <v>1.275594364465271</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.6278150725137055</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.516385237000554</v>
+        <v>2.611113217698392</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735835647412096</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.808413972595499</v>
+        <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
         <v>-4.261859222138038</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.103313859426536</v>
+        <v>1.198041840124374</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.6100456135827499</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.442386604445849</v>
+        <v>2.537114585143687</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762643902144509</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.830814465918065</v>
+        <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
         <v>-4.175059724359029</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.160434151860706</v>
+        <v>1.255162132558544</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.6100456135827499</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.464787097768415</v>
+        <v>2.559515078466253</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729142822900688</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.830886867291477</v>
+        <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
         <v>-4.075367109630017</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.200383599125723</v>
+        <v>1.295111579823561</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.5103529988537381</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.524675067979234</v>
+        <v>2.619403048677072</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743216620473594</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.841893789766179</v>
+        <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
         <v>-4.143737295954027</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.184042447070821</v>
+        <v>1.278770427768659</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.5010772998175231</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.541247409875665</v>
+        <v>2.635975390573503</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714175563978363</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.83233049839807</v>
+        <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
         <v>-4.022320866327551</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.223045727553303</v>
+        <v>1.317773708251141</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.5010772998175231</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.531684118507556</v>
+        <v>2.626412099205395</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710903155887697</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.657040063438457</v>
+        <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
         <v>-4.053314025656256</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.035358028862207</v>
+        <v>1.130086009560046</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.5010772998175231</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.356393683547943</v>
+        <v>2.451121664245782</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746038950675894</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.661607295430245</v>
+        <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
         <v>-3.877839765863787</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.110114964770983</v>
+        <v>1.204842945468821</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.5010772998175231</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.360960915539731</v>
+        <v>2.455688896237569</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.76502074769544</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.661618769317042</v>
+        <v>2.756346750014881</v>
       </c>
       <c r="D1940" t="n">
         <v>-3.988776018505035</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.065751937601281</v>
+        <v>1.160479918299119</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.5010772998175231</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.360972389426529</v>
+        <v>2.455700370124367</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773206721581285</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.664750154536948</v>
+        <v>2.759478135234786</v>
       </c>
       <c r="D1941" t="n">
         <v>-4.191802596048269</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9876726918038932</v>
+        <v>1.082400672501731</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.7041038773607566</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.242287828120494</v>
+        <v>2.337015808818332</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784340376734155</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.67492254096908</v>
+        <v>2.769650521666918</v>
       </c>
       <c r="D1942" t="n">
         <v>-4.033876997112976</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.061015317810143</v>
+        <v>1.155743298507981</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.7041038773607566</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.252460214552626</v>
+        <v>2.347188195250465</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,45 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.812548696413794</v>
+        <v>3.786946382212292</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.669868811542941</v>
+        <v>2.764596792240779</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.182198250924104</v>
+        <v>-4.029151711417048</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9966330868595517</v>
+        <v>1.152579683360212</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.7041038773607566</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.247406485126487</v>
+        <v>2.342134465824325</v>
+      </c>
+    </row>
+    <row r="1944">
+      <c r="A1944" s="2" t="n">
+        <v>45406</v>
+      </c>
+      <c r="B1944" t="n">
+        <v>3.858721393494696</v>
+      </c>
+      <c r="C1944" t="n">
+        <v>2.958209790711423</v>
+      </c>
+      <c r="D1944" t="n">
+        <v>-4.029151711417048</v>
+      </c>
+      <c r="E1944" t="n">
+        <v>1.152579683360212</v>
+      </c>
+      <c r="F1944" t="n">
+        <v>-0.7041038773607566</v>
+      </c>
+      <c r="G1944" t="n">
+        <v>2.951273587697791</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240424.xlsx
+++ b/tame_output/ON/bt/strategyON_20240424.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>28.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,27 +819,27 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-30.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-41.9%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.7%</t>
+          <t>-79.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.5%</t>
+          <t>135.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>94.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-76.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-280.5%</t>
+          <t>-278.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-564.5%</t>
+          <t>-587.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-34.5%</t>
+          <t>-51.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-261.0%</t>
+          <t>-279.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-34.7%</t>
+          <t>-34.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-28.4%</t>
+          <t>-28.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-167.2%</t>
+          <t>-167.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-294.4%</t>
+          <t>-293.3%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,37 +1476,37 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-150.9%</t>
+          <t>-177.0%</t>
         </is>
       </c>
     </row>
@@ -45340,19 +45340,19 @@
         <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.152965457527332</v>
+        <v>3.058237476829494</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.964806701605866</v>
+        <v>-9.045156823082531</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4333136474287613</v>
+        <v>-0.5601816767172654</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.677622451149987</v>
+        <v>-2.666871918240684</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.546391986837341</v>
+        <v>1.458114325885084</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.763178672860424</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.14833294427436</v>
+        <v>3.053604963576521</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.832531227974979</v>
+        <v>-8.912881349451643</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3850359712293794</v>
+        <v>-0.5119040005178834</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.5453469775191</v>
+        <v>-2.534596444609797</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.6211247577629</v>
+        <v>1.532847096810643</v>
       </c>
     </row>
     <row r="1906">
@@ -45386,19 +45386,19 @@
         <v>3.78471521857595</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.151148004961996</v>
+        <v>3.056420024264158</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.641931553301825</v>
+        <v>-8.72228167477849</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3059810406724814</v>
+        <v>-0.4328490699609855</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.354747302845948</v>
+        <v>-2.343996769936644</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.738299623254428</v>
+        <v>1.650021962302172</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753878996430984</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.164054346185655</v>
+        <v>3.069326365487817</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.392931754618244</v>
+        <v>-8.473281876094909</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1934747799753902</v>
+        <v>-0.3203428092638942</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.354747302845948</v>
+        <v>-2.343996769936644</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.751205964478087</v>
+        <v>1.66292830352583</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692928280077641</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.036078416586436</v>
+        <v>2.941350435888598</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.498521744391349</v>
+        <v>-8.578871865868013</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3636867054838504</v>
+        <v>-0.4905547347723545</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.460337292619052</v>
+        <v>-2.449586759709749</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.559876041015005</v>
+        <v>1.471598380062749</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770419008457898</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.084622758463523</v>
+        <v>2.989894777765684</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.517256646509946</v>
+        <v>-8.59760676798661</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3226363244542032</v>
+        <v>-0.4495043537427073</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.460337292619052</v>
+        <v>-2.449586759709749</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.608420382892092</v>
+        <v>1.520142721939835</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.760330111180806</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.964743835775355</v>
+        <v>2.870015855077517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.369316605102346</v>
+        <v>-8.449666726579011</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.3833392305793311</v>
+        <v>-0.5102072598678351</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.440016376710494</v>
+        <v>-2.429265843801191</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.500734009749059</v>
+        <v>1.412456348796802</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723562653879199</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.956029849521877</v>
+        <v>2.861301868824039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.242424198667276</v>
+        <v>-8.322774320143941</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.341296254258781</v>
+        <v>-0.468164283547285</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.313123970275424</v>
+        <v>-2.302373437366121</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.568155467356622</v>
+        <v>1.479877806404366</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.729966140568103</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.949069237426784</v>
+        <v>2.854341256728945</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.198875791896585</v>
+        <v>-8.279225913373249</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3308375036455975</v>
+        <v>-0.4577055329341015</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.313123970275424</v>
+        <v>-2.302373437366121</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.561194855261529</v>
+        <v>1.472917194309273</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782918957963414</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.963531591807927</v>
+        <v>2.868803611110089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.956727398442727</v>
+        <v>-8.037077519919391</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2195157918829111</v>
+        <v>-0.3463838211714152</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.313123970275424</v>
+        <v>-2.302373437366121</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.575657209642672</v>
+        <v>1.487379548690416</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828547911192812</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.958063712267122</v>
+        <v>2.863335731569284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.893498026674378</v>
+        <v>-7.973848148151043</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1996919227163767</v>
+        <v>-0.3265599520048807</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.313123970275424</v>
+        <v>-2.302373437366121</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.570189330101867</v>
+        <v>1.481911669149611</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828049353262042</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.955561806277699</v>
+        <v>2.86083382557986</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.707010334297372</v>
+        <v>-7.787360455774037</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1275987517549977</v>
+        <v>-0.2544667810435017</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.126636277898418</v>
+        <v>-2.115885744989115</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.679580039538648</v>
+        <v>1.591302378586392</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812450103389904</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.963262784515024</v>
+        <v>2.868534803817186</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.685861135393929</v>
+        <v>-7.766211256870593</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1114380939562949</v>
+        <v>-0.2383061232447989</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.105487078994975</v>
+        <v>-2.094736546085672</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.699970537118039</v>
+        <v>1.611692876165783</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748324832788088</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.959043492862075</v>
+        <v>2.864315512164236</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.442095693410485</v>
+        <v>-7.522445814887149</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.01815120881586685</v>
+        <v>-0.1450192381043709</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.105487078994975</v>
+        <v>-2.094736546085672</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.69575124546509</v>
+        <v>1.607473584512834</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824307657527521</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.961167806782091</v>
+        <v>2.866439826084252</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.178067626217224</v>
+        <v>-7.258417747693889</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.08958433198145332</v>
+        <v>-0.03728369730705072</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.903621680179021</v>
+        <v>-1.892871147269718</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.818994798674678</v>
+        <v>1.730717137722422</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826351398749178</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.953909881765793</v>
+        <v>2.859181901067954</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.92821723226815</v>
+        <v>-7.008567353744814</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1822665645447854</v>
+        <v>0.05539853525628136</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.903621680179021</v>
+        <v>-1.892871147269718</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.81173687365838</v>
+        <v>1.723459212706124</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835954411481492</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.957509005286441</v>
+        <v>2.862781024588603</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.624649743264171</v>
+        <v>-6.704999864740835</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3072926836670256</v>
+        <v>0.1804246543785215</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.903621680179021</v>
+        <v>-1.892871147269718</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.815335997179029</v>
+        <v>1.727058336226773</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780930335862981</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.970836511340995</v>
+        <v>2.876108530643157</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.551169834412157</v>
+        <v>-6.631519955888821</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.350012153262385</v>
+        <v>0.2231441239738809</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.830141771327007</v>
+        <v>-1.819391238417704</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.872751448544791</v>
+        <v>1.784473787592535</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773761647102775</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.969856988957292</v>
+        <v>2.875129008259454</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.326136834743334</v>
+        <v>-6.406486956219998</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4390458307462111</v>
+        <v>0.312177801457707</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.605108771658184</v>
+        <v>-1.594358238748881</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.006791725962382</v>
+        <v>1.918514065010126</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764614304353067</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.974551790011609</v>
+        <v>2.879823809313771</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.111502457106927</v>
+        <v>-6.191852578583592</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5295943828550911</v>
+        <v>0.402726353566587</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.390474394021777</v>
+        <v>-1.379723861112474</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.140267153598543</v>
+        <v>2.051989492646287</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.798811195544776</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.955746048795405</v>
+        <v>2.861018068097567</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.844902100132575</v>
+        <v>-5.92525222160924</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6174287844286277</v>
+        <v>0.4905607551401236</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.390474394021777</v>
+        <v>-1.379723861112474</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.121461412382339</v>
+        <v>2.033183751430083</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797691308712288</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.957489125420282</v>
+        <v>2.862761144722444</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.604471603327715</v>
+        <v>-5.68482172480438</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.715344059775449</v>
+        <v>0.588476030486945</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.150043897216917</v>
+        <v>-1.139293364307614</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.267462787090133</v>
+        <v>2.179185126137876</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.821589933837679</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.961418439255103</v>
+        <v>2.866690458557264</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.36168079567827</v>
+        <v>-5.442030917154934</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8163896966700475</v>
+        <v>0.6895216673815434</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.150043897216917</v>
+        <v>-1.139293364307614</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.271392100924953</v>
+        <v>2.183114439972696</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.82232342234996</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.962097023172443</v>
+        <v>2.867369042474604</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.245740946053084</v>
+        <v>-5.326091067529749</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8634442204374615</v>
+        <v>0.7365761911489574</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.073222166200793</v>
+        <v>-1.06247163329149</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.318163723451967</v>
+        <v>2.229886062499711</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.848613050972333</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.959095094392436</v>
+        <v>2.864367113694598</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.003085357629921</v>
+        <v>-5.083435479106585</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9575045270267206</v>
+        <v>0.8306364977382166</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.073222166200793</v>
+        <v>-1.06247163329149</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.31516179467196</v>
+        <v>2.226884133719704</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818665376145932</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.96067413140305</v>
+        <v>2.865946150705212</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.78306455959291</v>
+        <v>-4.863414681069575</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.047091883252139</v>
+        <v>0.9202238539636349</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.9320023211328128</v>
+        <v>-0.9212517882235096</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.401472738723363</v>
+        <v>2.313195077771106</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.843270952009944</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.976568314204874</v>
+        <v>2.881840333507035</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.583815929688101</v>
+        <v>-4.664166051164766</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.142685518015886</v>
+        <v>1.015817488727382</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.9320023211328128</v>
+        <v>-0.9212517882235096</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.417366921525186</v>
+        <v>2.32908926057293</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845043810966252</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.977714158645175</v>
+        <v>2.882986177947337</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.424300826168731</v>
+        <v>-4.504650947645396</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.207637403863936</v>
+        <v>1.080769374575432</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.7724872176134429</v>
+        <v>-0.7617366847041397</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.51422182807711</v>
+        <v>2.425944167124854</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791269976046989</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.987802261206615</v>
+        <v>2.893074280508777</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.279628681068994</v>
+        <v>-4.359978802545658</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.275594364465271</v>
+        <v>1.148726335176766</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.6278150725137055</v>
+        <v>-0.6170645396044023</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.611113217698392</v>
+        <v>2.522835556746136</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735835647412096</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.903141953293337</v>
+        <v>2.808413972595499</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.261859222138038</v>
+        <v>-4.342209343614702</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.198041840124374</v>
+        <v>1.07117381083587</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.6100456135827499</v>
+        <v>-0.5992950806734467</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.537114585143687</v>
+        <v>2.448836924191431</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762643902144509</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.925542446615903</v>
+        <v>2.830814465918065</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.175059724359029</v>
+        <v>-4.255409845835693</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.255162132558544</v>
+        <v>1.12829410327004</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.6100456135827499</v>
+        <v>-0.5992950806734467</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.559515078466253</v>
+        <v>2.471237417513997</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729142822900688</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.925614847989315</v>
+        <v>2.830886867291477</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.075367109630017</v>
+        <v>-4.155717231106681</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.295111579823561</v>
+        <v>1.168243550535057</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.5103529988537381</v>
+        <v>-0.499602465944435</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.619403048677072</v>
+        <v>2.531125387724816</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743216620473594</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.936621770464017</v>
+        <v>2.841893789766179</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.143737295954027</v>
+        <v>-4.224087417430692</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.278770427768659</v>
+        <v>1.151902398480155</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.5010772998175231</v>
+        <v>-0.49032676690822</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.635975390573503</v>
+        <v>2.547697729621247</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714175563978363</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.927058479095908</v>
+        <v>2.83233049839807</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.022320866327551</v>
+        <v>-4.102670987804215</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.317773708251141</v>
+        <v>1.190905678962637</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.5010772998175231</v>
+        <v>-0.49032676690822</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.626412099205395</v>
+        <v>2.538134438253139</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710903155887697</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.751768044136295</v>
+        <v>2.657040063438457</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.053314025656256</v>
+        <v>-4.133664147132921</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.130086009560046</v>
+        <v>1.003217980271542</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.5010772998175231</v>
+        <v>-0.49032676690822</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.451121664245782</v>
+        <v>2.362844003293525</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746038950675894</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.756335276128083</v>
+        <v>2.661607295430245</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.877839765863787</v>
+        <v>-3.958189887340451</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.204842945468821</v>
+        <v>1.077974916180317</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.5010772998175231</v>
+        <v>-0.49032676690822</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.455688896237569</v>
+        <v>2.367411235285313</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.76502074769544</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.756346750014881</v>
+        <v>2.661618769317042</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.988776018505035</v>
+        <v>-4.0691261399817</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.160479918299119</v>
+        <v>1.033611889010615</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.5010772998175231</v>
+        <v>-0.49032676690822</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.455700370124367</v>
+        <v>2.367422709172111</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773206721581285</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.759478135234786</v>
+        <v>2.664750154536948</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.191802596048269</v>
+        <v>-4.272152717524933</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.082400672501731</v>
+        <v>0.9555326432132274</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.7041038773607566</v>
+        <v>-0.6933533444514535</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.337015808818332</v>
+        <v>2.248738147866076</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784340376734155</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.769650521666918</v>
+        <v>2.67492254096908</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.033876997112976</v>
+        <v>-4.11422711858964</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.155743298507981</v>
+        <v>1.028875269219477</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.7041038773607566</v>
+        <v>-0.6933533444514535</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.347188195250465</v>
+        <v>2.258910534298209</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786946382212292</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.764596792240779</v>
+        <v>2.669868811542941</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.029151711417048</v>
+        <v>-4.262548372400769</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.152579683360212</v>
+        <v>0.9644930382688859</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.7041038773607566</v>
+        <v>-0.6933533444514535</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.342134465824325</v>
+        <v>2.253856804872069</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.858721393494696</v>
+        <v>3.562266635862971</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.958209790711423</v>
+        <v>2.696931144350441</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.029151711417048</v>
+        <v>-4.262548372400769</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.152579683360212</v>
+        <v>0.9644930382688859</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.7041038773607566</v>
+        <v>-0.6933533444514535</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.951273587697791</v>
+        <v>2.689994941336809</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240424.xlsx
+++ b/tame_output/ON/bt/strategyON_20240424.xlsx
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,15 +811,15 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-30.3%</t>
+          <t>-29.1%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-41.9%</t>
+          <t>-45.0%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.6%</t>
+          <t>-79.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.9%</t>
+          <t>94.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.0%</t>
+          <t>-76.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-587.8%</t>
+          <t>-589.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-51.2%</t>
+          <t>-38.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-279.8%</t>
+          <t>-271.1%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-34.6%</t>
+          <t>-34.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-28.8%</t>
+          <t>-28.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-293.3%</t>
+          <t>-294.0%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-177.0%</t>
+          <t>-180.1%</t>
         </is>
       </c>
     </row>
@@ -45340,19 +45340,19 @@
         <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.058237476829494</v>
+        <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.045156823082531</v>
+        <v>-9.066337586237708</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5601816767172654</v>
+        <v>-0.4739260012814981</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.666871918240684</v>
+        <v>-2.673678011017797</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.458114325885084</v>
+        <v>1.548758650916655</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.763178672860424</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.053604963576521</v>
+        <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.912881349451643</v>
+        <v>-8.934062112606821</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.5119040005178834</v>
+        <v>-0.4256483250821161</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.534596444609797</v>
+        <v>-2.54140253738691</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.532847096810643</v>
+        <v>1.623491421842214</v>
       </c>
     </row>
     <row r="1906">
@@ -45386,19 +45386,19 @@
         <v>3.78471521857595</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.056420024264158</v>
+        <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.72228167477849</v>
+        <v>-8.743462437933667</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4328490699609855</v>
+        <v>-0.3465933945252182</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.343996769936644</v>
+        <v>-2.350802862713758</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.650021962302172</v>
+        <v>1.740666287333742</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753878996430984</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.069326365487817</v>
+        <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.473281876094909</v>
+        <v>-8.494462639250086</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.3203428092638942</v>
+        <v>-0.234087133828127</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.343996769936644</v>
+        <v>-2.350802862713758</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.66292830352583</v>
+        <v>1.753572628557401</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692928280077641</v>
       </c>
       <c r="C1908" t="n">
-        <v>2.941350435888598</v>
+        <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.578871865868013</v>
+        <v>-8.600052629023191</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4905547347723545</v>
+        <v>-0.4042990593365872</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.449586759709749</v>
+        <v>-2.456392852486862</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.471598380062749</v>
+        <v>1.562242705094319</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770419008457898</v>
       </c>
       <c r="C1909" t="n">
-        <v>2.989894777765684</v>
+        <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.59760676798661</v>
+        <v>-8.618787531141788</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4495043537427073</v>
+        <v>-0.36324867830694</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.449586759709749</v>
+        <v>-2.456392852486862</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.520142721939835</v>
+        <v>1.610787046971406</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.760330111180806</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.870015855077517</v>
+        <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.449666726579011</v>
+        <v>-8.470847489734188</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.5102072598678351</v>
+        <v>-0.4239515844320678</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.429265843801191</v>
+        <v>-2.436071936578304</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.412456348796802</v>
+        <v>1.503100673828373</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723562653879199</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.861301868824039</v>
+        <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.322774320143941</v>
+        <v>-8.343955083299118</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.468164283547285</v>
+        <v>-0.3819086081115177</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.302373437366121</v>
+        <v>-2.309179530143235</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.479877806404366</v>
+        <v>1.570522131435937</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.729966140568103</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.854341256728945</v>
+        <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.279225913373249</v>
+        <v>-8.300406676528427</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4577055329341015</v>
+        <v>-0.3714498574983343</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.302373437366121</v>
+        <v>-2.309179530143235</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.472917194309273</v>
+        <v>1.563561519340843</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782918957963414</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.868803611110089</v>
+        <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.037077519919391</v>
+        <v>-8.058258283074569</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3463838211714152</v>
+        <v>-0.2601281457356479</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.302373437366121</v>
+        <v>-2.309179530143235</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.487379548690416</v>
+        <v>1.578023873721986</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828547911192812</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.863335731569284</v>
+        <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.973848148151043</v>
+        <v>-7.99502891130622</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3265599520048807</v>
+        <v>-0.2403042765691135</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.302373437366121</v>
+        <v>-2.309179530143235</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.481911669149611</v>
+        <v>1.572555994181182</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828049353262042</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.86083382557986</v>
+        <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.787360455774037</v>
+        <v>-7.808541218929214</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2544667810435017</v>
+        <v>-0.1682111056077344</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.115885744989115</v>
+        <v>-2.122691837766228</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.591302378586392</v>
+        <v>1.681946703617962</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812450103389904</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.868534803817186</v>
+        <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.766211256870593</v>
+        <v>-7.787392020025771</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2383061232447989</v>
+        <v>-0.1520504478090317</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.094736546085672</v>
+        <v>-2.101542638862785</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.611692876165783</v>
+        <v>1.702337201197353</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748324832788088</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.864315512164236</v>
+        <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.522445814887149</v>
+        <v>-7.543626578042327</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1450192381043709</v>
+        <v>-0.05876356266860361</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.094736546085672</v>
+        <v>-2.101542638862785</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.607473584512834</v>
+        <v>1.698117909544404</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824307657527521</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.866439826084252</v>
+        <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.258417747693889</v>
+        <v>-7.279598510849066</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.03728369730705072</v>
+        <v>0.04897197812871656</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.892871147269718</v>
+        <v>-1.899677240046831</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.730717137722422</v>
+        <v>1.821361462753992</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826351398749178</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.859181901067954</v>
+        <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.008567353744814</v>
+        <v>-7.029748116899992</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.05539853525628136</v>
+        <v>0.1416542106920486</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.892871147269718</v>
+        <v>-1.899677240046831</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.723459212706124</v>
+        <v>1.814103537737694</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835954411481492</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.862781024588603</v>
+        <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.704999864740835</v>
+        <v>-6.726180627896013</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1804246543785215</v>
+        <v>0.2666803298142888</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.892871147269718</v>
+        <v>-1.899677240046831</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.727058336226773</v>
+        <v>1.817702661258343</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780930335862981</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.876108530643157</v>
+        <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.631519955888821</v>
+        <v>-6.652700719043999</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2231441239738809</v>
+        <v>0.3093997994096482</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.819391238417704</v>
+        <v>-1.826197331194817</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.784473787592535</v>
+        <v>1.875118112624105</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773761647102775</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.875129008259454</v>
+        <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.406486956219998</v>
+        <v>-6.427667719375176</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.312177801457707</v>
+        <v>0.3984334768934743</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.594358238748881</v>
+        <v>-1.601164331525994</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.918514065010126</v>
+        <v>2.009158390041696</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764614304353067</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.879823809313771</v>
+        <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.191852578583592</v>
+        <v>-6.213033341738769</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.402726353566587</v>
+        <v>0.4889820290023543</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.379723861112474</v>
+        <v>-1.386529953889587</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.051989492646287</v>
+        <v>2.142633817677857</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.798811195544776</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.861018068097567</v>
+        <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.92525222160924</v>
+        <v>-5.946432984764417</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4905607551401236</v>
+        <v>0.5768164305758909</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.379723861112474</v>
+        <v>-1.386529953889587</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.033183751430083</v>
+        <v>2.123828076461653</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797691308712288</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.862761144722444</v>
+        <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.68482172480438</v>
+        <v>-5.706002487959557</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.588476030486945</v>
+        <v>0.6747317059227123</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.139293364307614</v>
+        <v>-1.146099457084727</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.179185126137876</v>
+        <v>2.269829451169446</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.821589933837679</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.866690458557264</v>
+        <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.442030917154934</v>
+        <v>-5.463211680310112</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6895216673815434</v>
+        <v>0.7757773428173107</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.139293364307614</v>
+        <v>-1.146099457084727</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.183114439972696</v>
+        <v>2.273758765004267</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.82232342234996</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.867369042474604</v>
+        <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.326091067529749</v>
+        <v>-5.347271830684926</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7365761911489574</v>
+        <v>0.8228318665847247</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.06247163329149</v>
+        <v>-1.069277726068603</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.229886062499711</v>
+        <v>2.320530387531281</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.848613050972333</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.864367113694598</v>
+        <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.083435479106585</v>
+        <v>-5.104616242261763</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8306364977382166</v>
+        <v>0.9168921731739839</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.06247163329149</v>
+        <v>-1.069277726068603</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.226884133719704</v>
+        <v>2.317528458751275</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818665376145932</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.865946150705212</v>
+        <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.863414681069575</v>
+        <v>-4.884595444224752</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9202238539636349</v>
+        <v>1.006479529399402</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.9212517882235096</v>
+        <v>-0.9280578810006228</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.313195077771106</v>
+        <v>2.403839402802677</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.843270952009944</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.881840333507035</v>
+        <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.664166051164766</v>
+        <v>-4.685346814319943</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.015817488727382</v>
+        <v>1.102073164163149</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.9212517882235096</v>
+        <v>-0.9280578810006228</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.32908926057293</v>
+        <v>2.4197335856045</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845043810966252</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.882986177947337</v>
+        <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.504650947645396</v>
+        <v>-4.525831710800573</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.080769374575432</v>
+        <v>1.167025050011199</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.7617366847041397</v>
+        <v>-0.7685427774812529</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.425944167124854</v>
+        <v>2.516588492156424</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791269976046989</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.893074280508777</v>
+        <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.359978802545658</v>
+        <v>-4.381159565700836</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.148726335176766</v>
+        <v>1.234982010612534</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.6170645396044023</v>
+        <v>-0.6238706323815155</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.522835556746136</v>
+        <v>2.613479881777706</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735835647412096</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.808413972595499</v>
+        <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.342209343614702</v>
+        <v>-4.36339010676988</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.07117381083587</v>
+        <v>1.157429486271638</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.5992950806734467</v>
+        <v>-0.6061011734505599</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.448836924191431</v>
+        <v>2.539481249223001</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762643902144509</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.830814465918065</v>
+        <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.255409845835693</v>
+        <v>-4.276590608990871</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.12829410327004</v>
+        <v>1.214549778705807</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.5992950806734467</v>
+        <v>-0.6061011734505599</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.471237417513997</v>
+        <v>2.561881742545567</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729142822900688</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.830886867291477</v>
+        <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.155717231106681</v>
+        <v>-4.176897994261859</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.168243550535057</v>
+        <v>1.254499225970824</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.499602465944435</v>
+        <v>-0.5064085587215481</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.531125387724816</v>
+        <v>2.621769712756386</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743216620473594</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.841893789766179</v>
+        <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.224087417430692</v>
+        <v>-4.245268180585869</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.151902398480155</v>
+        <v>1.238158073915922</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.49032676690822</v>
+        <v>-0.4971328596853332</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.547697729621247</v>
+        <v>2.638342054652818</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714175563978363</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.83233049839807</v>
+        <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.102670987804215</v>
+        <v>-4.123851750959393</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.190905678962637</v>
+        <v>1.277161354398404</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.49032676690822</v>
+        <v>-0.4971328596853332</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.538134438253139</v>
+        <v>2.628778763284709</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710903155887697</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.657040063438457</v>
+        <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.133664147132921</v>
+        <v>-4.154844910288098</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.003217980271542</v>
+        <v>1.089473655707309</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.49032676690822</v>
+        <v>-0.4971328596853332</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.362844003293525</v>
+        <v>2.453488328325096</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746038950675894</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.661607295430245</v>
+        <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.958189887340451</v>
+        <v>-3.979370650495629</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.077974916180317</v>
+        <v>1.164230591616084</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.49032676690822</v>
+        <v>-0.4971328596853332</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.367411235285313</v>
+        <v>2.458055560316883</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.76502074769544</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.661618769317042</v>
+        <v>2.756346750014881</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.0691261399817</v>
+        <v>-4.090306903136877</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.033611889010615</v>
+        <v>1.119867564446382</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.49032676690822</v>
+        <v>-0.4971328596853332</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.367422709172111</v>
+        <v>2.458067034203681</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773206721581285</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.664750154536948</v>
+        <v>2.759478135234786</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.272152717524933</v>
+        <v>-4.29333348068011</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9555326432132274</v>
+        <v>1.041788318648995</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.6933533444514535</v>
+        <v>-0.7001594372285667</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.248738147866076</v>
+        <v>2.339382472897646</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784340376734155</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.67492254096908</v>
+        <v>2.769650521666918</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.11422711858964</v>
+        <v>-4.135407881744817</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.028875269219477</v>
+        <v>1.115130944655244</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.6933533444514535</v>
+        <v>-0.7001594372285667</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.258910534298209</v>
+        <v>2.349554859329779</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786946382212292</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.669868811542941</v>
+        <v>2.764596792240779</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.262548372400769</v>
+        <v>-4.283729135555946</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9644930382688859</v>
+        <v>1.050748713704653</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.6933533444514535</v>
+        <v>-0.7001594372285667</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.253856804872069</v>
+        <v>2.344501129903639</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.562266635862971</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.696931144350441</v>
+        <v>2.666636672186587</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.262548372400769</v>
+        <v>-4.283729135555946</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9644930382688859</v>
+        <v>1.050748713704653</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.6933533444514535</v>
+        <v>-0.7001594372285667</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.689994941336809</v>
+        <v>2.659700469172955</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240424.xlsx
+++ b/tame_output/ON/bt/strategyON_20240424.xlsx
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705545</v>
+        <v>3.311607601705546</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045693</v>
+        <v>3.317575502045694</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078594</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628917</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240574</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085277</v>
+        <v>3.685157806085276</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.684840248282097</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116211</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081562</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425322</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702408</v>
+        <v>3.747699084702406</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906222</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781945</v>
+        <v>3.784680945781943</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567241</v>
+        <v>3.800825778567239</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78930753648777</v>
+        <v>3.789307536487768</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309722</v>
+        <v>3.833249172309721</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858725</v>
+        <v>3.839370871858724</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85615817609647</v>
+        <v>3.856158176096469</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761805</v>
+        <v>3.787326853761804</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255781</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860424</v>
+        <v>3.763178672860422</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471521857595</v>
+        <v>3.784715218575948</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430984</v>
+        <v>3.753878996430982</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077641</v>
+        <v>3.692928280077639</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457898</v>
+        <v>3.770419008457896</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180806</v>
+        <v>3.760330111180805</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879199</v>
+        <v>3.723562653879198</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568103</v>
+        <v>3.729966140568102</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963414</v>
+        <v>3.782918957963413</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192812</v>
+        <v>3.828547911192811</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966252</v>
+        <v>3.845043810966253</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>

--- a/tame_output/ON/bt/strategyON_20240424.xlsx
+++ b/tame_output/ON/bt/strategyON_20240424.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>49.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,15 +811,15 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-45.0%</t>
+          <t>-36.0%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-79.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.1%</t>
+          <t>116.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.8%</t>
+          <t>135.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.8%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-685.6%</t>
+          <t>-678.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-56.9%</t>
+          <t>-56.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.1%</t>
+          <t>-75.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>96.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-278.9%</t>
+          <t>-280.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-589.9%</t>
+          <t>-583.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.5%</t>
+          <t>-44.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-38.4%</t>
+          <t>-31.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-271.1%</t>
+          <t>-269.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-34.7%</t>
+          <t>-36.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.8%</t>
+          <t>-38.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-28.9%</t>
+          <t>-30.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-294.0%</t>
+          <t>-306.8%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-180.1%</t>
+          <t>-220.1%</t>
         </is>
       </c>
     </row>
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705546</v>
+        <v>3.311607601705545</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045694</v>
+        <v>3.317575502045693</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43750,7 +43750,7 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831154</v>
+        <v>3.320996253831153</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279814</v>
+        <v>3.385382209279813</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511406</v>
+        <v>3.367379938511404</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386095</v>
+        <v>3.376932391386094</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611695</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.71306995552271</v>
+        <v>-10.63660856405147</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.148157870589155</v>
+        <v>-1.117573314000662</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.90578972056602</v>
+        <v>-2.91455606117594</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.393952703594063</v>
+        <v>1.388692899228111</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199885</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.93110772715388</v>
+        <v>-10.85464633568265</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.230890424757189</v>
+        <v>-1.200305868168698</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.080560488661919</v>
+        <v>-3.089326829271839</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.29357279722096</v>
+        <v>1.288312992855008</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.85763789548643</v>
+        <v>-10.7811765040152</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.186130790596789</v>
+        <v>-1.155546234008296</v>
       </c>
       <c r="F1880" t="n">
-        <v>-3.00709065699447</v>
+        <v>-3.01585699760439</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.35302639771485</v>
+        <v>1.347766593348898</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078594</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.03276231287298</v>
+        <v>-10.95630092140175</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.24162533680389</v>
+        <v>-1.211040780215397</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.182215074381014</v>
+        <v>-3.190981414990934</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.262506968030441</v>
+        <v>1.257247163664489</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.26721440688747</v>
+        <v>-11.19075301541624</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.342625339311282</v>
+        <v>-1.312040782722789</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.182215074381014</v>
+        <v>-3.190981414990934</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.255287803128845</v>
+        <v>1.250027998762893</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.55501825142471</v>
+        <v>-11.47855685995347</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.464419067900153</v>
+        <v>-1.433834511311661</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.470018918918252</v>
+        <v>-3.478785259528172</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.075933305632526</v>
+        <v>1.070673501266574</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.493712438860584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.78484269858853</v>
+        <v>-11.7083813071173</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.555233056927126</v>
+        <v>-1.524648500338635</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.632666455988413</v>
+        <v>-3.641432796598333</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9794605732289856</v>
+        <v>0.9742007688630339</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.01687161832479</v>
+        <v>-11.94041022685356</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.645350896192517</v>
+        <v>-1.614766339604025</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.694679153176836</v>
+        <v>-3.703445493786756</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9449466835450462</v>
+        <v>0.9396868791790944</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.96485610435598</v>
+        <v>-11.88839471288475</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.620554354918591</v>
+        <v>-1.589969798330098</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.694679153176836</v>
+        <v>-3.703445493786756</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.948937019231447</v>
+        <v>0.9436772148654953</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.600034689628919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.1065279460801</v>
+        <v>-12.03006655460887</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.678698318506981</v>
+        <v>-1.648113761918489</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.694679153176836</v>
+        <v>-3.703445493786756</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9474617923327053</v>
+        <v>0.9422019879667536</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.20543468653938</v>
+        <v>-12.12897329506814</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.703207604525818</v>
+        <v>-1.672623047937326</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.793585893636112</v>
+        <v>-3.802352234246031</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9031711582220123</v>
+        <v>0.8979113538560606</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240574</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.00628257930228</v>
+        <v>-11.92982118783105</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.636597895277661</v>
+        <v>-1.60601333868917</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.628263367686298</v>
+        <v>-3.637029708296218</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9893135401452176</v>
+        <v>0.9840537357792658</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085276</v>
+        <v>3.685157806085277</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.78043742658286</v>
+        <v>-11.70397603511163</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.536680761153689</v>
+        <v>-1.506096204565196</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.586336692099135</v>
+        <v>-3.595103032709054</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.024048618533724</v>
+        <v>1.018788814167773</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282097</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.49416261426017</v>
+        <v>-11.41770122278894</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.421031691668551</v>
+        <v>-1.39044713508006</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.586336692099135</v>
+        <v>-3.595103032709054</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.025187763089783</v>
+        <v>1.019927958723831</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116211</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.54705790230446</v>
+        <v>-11.47059651083323</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.439556032724158</v>
+        <v>-1.408971476135666</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.581381346010688</v>
+        <v>-3.590147686620608</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.030794744904958</v>
+        <v>1.025534940539007</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081562</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.26314917137571</v>
+        <v>-11.18668777990448</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.320258836114022</v>
+        <v>-1.28967427952553</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.581381346010688</v>
+        <v>-3.590147686620608</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.036528449143595</v>
+        <v>1.031268644777643</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425322</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.14772824723761</v>
+        <v>-11.07126685576638</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.283827728852649</v>
+        <v>-1.253243172264157</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.465960421872593</v>
+        <v>-3.474726762482512</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.096043741232587</v>
+        <v>1.090783936866635</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702406</v>
+        <v>3.747699084702408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.88389138003354</v>
+        <v>-10.80742998856231</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.188176463283928</v>
+        <v>-1.157591906695437</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.465960421872593</v>
+        <v>-3.474726762482512</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.08616025991968</v>
+        <v>1.080900455553728</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906222</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.61664957916514</v>
+        <v>-10.54018818769391</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.083114303435944</v>
+        <v>-1.052529746847451</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.465960421872593</v>
+        <v>-3.474726762482512</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.084325699420306</v>
+        <v>1.079065895054354</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781943</v>
+        <v>3.784680945781945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.49334365068692</v>
+        <v>-10.41688225921569</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.034092247018117</v>
+        <v>-1.003507690429624</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.37654275074503</v>
+        <v>-3.385309091354949</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.137675987123383</v>
+        <v>1.132416182757431</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567239</v>
+        <v>3.800825778567241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.46939010971097</v>
+        <v>-10.39292871823974</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.02384232448224</v>
+        <v>-0.993257767893748</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.352589209769072</v>
+        <v>-3.361355550378992</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.152716617854451</v>
+        <v>1.147456813488499</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487768</v>
+        <v>3.78930753648777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.20533017138817</v>
+        <v>-10.12886877991694</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9314786653148737</v>
+        <v>-0.9008941087263809</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.088529271446276</v>
+        <v>-3.097295612056195</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.297892264686377</v>
+        <v>1.292632460320425</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309721</v>
+        <v>3.833249172309722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.498250547883332</v>
+        <v>-9.421789156412101</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6514338495732392</v>
+        <v>-0.6208492929847469</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.088529271446276</v>
+        <v>-3.097295612056195</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.295105231026076</v>
+        <v>1.289845426660124</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858724</v>
+        <v>3.839370871858725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.458066249517142</v>
+        <v>-9.381604858045911</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6350165063389217</v>
+        <v>-0.6044319497504294</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.048344973080085</v>
+        <v>-3.057111313690005</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.319559433933632</v>
+        <v>1.31429962956768</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096469</v>
+        <v>3.85615817609647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.377996453979337</v>
+        <v>-9.301535062508107</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6036217669030428</v>
+        <v>-0.5730372103145509</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.968275177542281</v>
+        <v>-2.977041518152201</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.366968132477071</v>
+        <v>1.361708328111119</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761804</v>
+        <v>3.787326853761805</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.14451523174974</v>
+        <v>-9.068053840278509</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5023048491733517</v>
+        <v>-0.4717202925848594</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.734793955312683</v>
+        <v>-2.743560295922602</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.514981294652682</v>
+        <v>1.509721490286731</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255781</v>
+        <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.066337586237708</v>
+        <v>-8.888345310134635</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4739260012814981</v>
+        <v>-0.402729090840269</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.673678011017797</v>
+        <v>-2.686388791759906</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.548758650916655</v>
+        <v>1.541132182471389</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860422</v>
+        <v>3.763178672860424</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.934062112606821</v>
+        <v>-8.756069836503748</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4256483250821161</v>
+        <v>-0.354451414640887</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.54140253738691</v>
+        <v>-2.55411331812902</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.623491421842214</v>
+        <v>1.615864953396948</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575948</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.743462437933667</v>
+        <v>-8.565470161830595</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3465933945252182</v>
+        <v>-0.2753964840839891</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.350802862713758</v>
+        <v>-2.363513643455867</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.740666287333742</v>
+        <v>1.733039818888476</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430982</v>
+        <v>3.753878996430985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.494462639250086</v>
+        <v>-8.316470363147014</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.234087133828127</v>
+        <v>-0.1628902233868978</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.350802862713758</v>
+        <v>-2.363513643455867</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.753572628557401</v>
+        <v>1.745946160112135</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077639</v>
+        <v>3.692928280077641</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.600052629023191</v>
+        <v>-8.422060352920118</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4042990593365872</v>
+        <v>-0.3331021488953585</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.456392852486862</v>
+        <v>-2.469103633228972</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.562242705094319</v>
+        <v>1.554616236649054</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457896</v>
+        <v>3.770419008457899</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.618787531141788</v>
+        <v>-8.440795255038715</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.36324867830694</v>
+        <v>-0.2920517678657109</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.456392852486862</v>
+        <v>-2.469103633228972</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.610787046971406</v>
+        <v>1.60316057852614</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180805</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.470847489734188</v>
+        <v>-8.292855213631116</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4239515844320678</v>
+        <v>-0.3527546739908387</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.436071936578304</v>
+        <v>-2.448782717320414</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.503100673828373</v>
+        <v>1.495474205383107</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879198</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.343955083299118</v>
+        <v>-8.165962807196046</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.3819086081115177</v>
+        <v>-0.3107116976702886</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.309179530143235</v>
+        <v>-2.321890310885344</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.570522131435937</v>
+        <v>1.562895662990671</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568102</v>
+        <v>3.729966140568105</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.300406676528427</v>
+        <v>-8.122414400425354</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3714498574983343</v>
+        <v>-0.3002529470571051</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.309179530143235</v>
+        <v>-2.321890310885344</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.563561519340843</v>
+        <v>1.555935050895578</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963413</v>
+        <v>3.782918957963416</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.058258283074569</v>
+        <v>-7.880266006971496</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2601281457356479</v>
+        <v>-0.1889312352944188</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.309179530143235</v>
+        <v>-2.321890310885344</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.578023873721986</v>
+        <v>1.570397405276721</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192811</v>
+        <v>3.828547911192814</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.99502891130622</v>
+        <v>-7.817036635203148</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2403042765691135</v>
+        <v>-0.1691073661278848</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.309179530143235</v>
+        <v>-2.321890310885344</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.572555994181182</v>
+        <v>1.564929525735916</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262042</v>
+        <v>3.828049353262044</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.808541218929214</v>
+        <v>-7.630548942826142</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1682111056077344</v>
+        <v>-0.09701419516650533</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.122691837766228</v>
+        <v>-2.135402618508337</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.681946703617962</v>
+        <v>1.674320235172696</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389904</v>
+        <v>3.812450103389906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.787392020025771</v>
+        <v>-7.609399743922698</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1520504478090317</v>
+        <v>-0.08085353736780299</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.101542638862785</v>
+        <v>-2.114253419604894</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.702337201197353</v>
+        <v>1.694710732752088</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788088</v>
+        <v>3.748324832788091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.543626578042327</v>
+        <v>-7.365634301939254</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.05876356266860361</v>
+        <v>0.0124333477726255</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.101542638862785</v>
+        <v>-2.114253419604894</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.698117909544404</v>
+        <v>1.690491441099139</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527521</v>
+        <v>3.824307657527523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.279598510849066</v>
+        <v>-7.101606234745994</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.04897197812871656</v>
+        <v>0.1201688885699457</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.899677240046831</v>
+        <v>-1.912388020788941</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.821361462753992</v>
+        <v>1.813734994308727</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749178</v>
+        <v>3.82635139874918</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.029748116899992</v>
+        <v>-6.851755840796919</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1416542106920486</v>
+        <v>0.2128511211332778</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.899677240046831</v>
+        <v>-1.912388020788941</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.814103537737694</v>
+        <v>1.806477069292429</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481492</v>
+        <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.726180627896013</v>
+        <v>-6.54818835179294</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2666803298142888</v>
+        <v>0.3378772402555179</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.899677240046831</v>
+        <v>-1.912388020788941</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.817702661258343</v>
+        <v>1.810076192813078</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862981</v>
+        <v>3.780930335862982</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.652700719043999</v>
+        <v>-6.474708442940926</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3093997994096482</v>
+        <v>0.3805967098508773</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.826197331194817</v>
+        <v>-1.838908111936926</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.875118112624105</v>
+        <v>1.86749164417884</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102775</v>
+        <v>3.773761647102777</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.427667719375176</v>
+        <v>-6.249675443272103</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3984334768934743</v>
+        <v>0.4696303873347034</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.601164331525994</v>
+        <v>-1.613875112268103</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.009158390041696</v>
+        <v>2.00153192159643</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353067</v>
+        <v>3.764614304353069</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.213033341738769</v>
+        <v>-6.035041065635697</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4889820290023543</v>
+        <v>0.5601789394435834</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.386529953889587</v>
+        <v>-1.399240734631697</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.142633817677857</v>
+        <v>2.135007349232592</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544776</v>
+        <v>3.798811195544777</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.946432984764417</v>
+        <v>-5.768440708661345</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5768164305758909</v>
+        <v>0.64801334101712</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.386529953889587</v>
+        <v>-1.399240734631697</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.123828076461653</v>
+        <v>2.116201608016387</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712288</v>
+        <v>3.79769130871229</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.706002487959557</v>
+        <v>-5.528010211856484</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6747317059227123</v>
+        <v>0.7459286163639414</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.146099457084727</v>
+        <v>-1.158810237826836</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.269829451169446</v>
+        <v>2.262202982724181</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837679</v>
+        <v>3.82158993383768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.463211680310112</v>
+        <v>-5.285219404207039</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7757773428173107</v>
+        <v>0.8469742532585398</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.146099457084727</v>
+        <v>-1.158810237826836</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.273758765004267</v>
+        <v>2.266132296559001</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232342234996</v>
+        <v>3.822323422349962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.347271830684926</v>
+        <v>-5.169279554581854</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8228318665847247</v>
+        <v>0.8940287770259538</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.069277726068603</v>
+        <v>-1.081988506810712</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.320530387531281</v>
+        <v>2.312903919086016</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972333</v>
+        <v>3.848613050972335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.104616242261763</v>
+        <v>-4.92662396615869</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9168921731739839</v>
+        <v>0.9880890836152127</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.069277726068603</v>
+        <v>-1.081988506810712</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.317528458751275</v>
+        <v>2.309901990306009</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145932</v>
+        <v>3.818665376145934</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.884595444224752</v>
+        <v>-4.70660316812168</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.006479529399402</v>
+        <v>1.077676439840631</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.9280578810006228</v>
+        <v>-0.9407686617427322</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.403839402802677</v>
+        <v>2.396212934357411</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009944</v>
+        <v>3.843270952009946</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.685346814319943</v>
+        <v>-4.50735453821687</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.102073164163149</v>
+        <v>1.173270074604378</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.9280578810006228</v>
+        <v>-0.9407686617427322</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.4197335856045</v>
+        <v>2.412107117159235</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966253</v>
+        <v>3.845043810966255</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.525831710800573</v>
+        <v>-4.347839434697501</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.167025050011199</v>
+        <v>1.238221960452428</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.7685427774812529</v>
+        <v>-0.7812535582233623</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.516588492156424</v>
+        <v>2.508962023711158</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046989</v>
+        <v>3.791269976046991</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.381159565700836</v>
+        <v>-4.203167289597763</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.234982010612534</v>
+        <v>1.306178921053763</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.6238706323815155</v>
+        <v>-0.6365814131236249</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.613479881777706</v>
+        <v>2.60585341333244</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412096</v>
+        <v>3.735835647412098</v>
       </c>
       <c r="C1933" t="n">
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.36339010676988</v>
+        <v>-4.185397830666807</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.157429486271638</v>
+        <v>1.228626396712867</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.6061011734505599</v>
+        <v>-0.6188119541926693</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.539481249223001</v>
+        <v>2.531854780777735</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144509</v>
+        <v>3.762643902144511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.276590608990871</v>
+        <v>-4.098598332887798</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.214549778705807</v>
+        <v>1.285746689147036</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.6061011734505599</v>
+        <v>-0.6188119541926693</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.561881742545567</v>
+        <v>2.554255274100302</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900688</v>
+        <v>3.729142822900689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.176897994261859</v>
+        <v>-3.998905718158786</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.254499225970824</v>
+        <v>1.325696136412053</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.5064085587215481</v>
+        <v>-0.5191193394636575</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.621769712756386</v>
+        <v>2.614143244311121</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473594</v>
+        <v>3.743216620473595</v>
       </c>
       <c r="C1936" t="n">
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.245268180585869</v>
+        <v>-4.067275904482797</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.238158073915922</v>
+        <v>1.309354984357151</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4971328596853332</v>
+        <v>-0.5098436404274426</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.638342054652818</v>
+        <v>2.630715586207552</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978363</v>
+        <v>3.714175563978364</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.123851750959393</v>
+        <v>-3.94585947485632</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.277161354398404</v>
+        <v>1.348358264839633</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4971328596853332</v>
+        <v>-0.5098436404274426</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.628778763284709</v>
+        <v>2.621152294839443</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.154844910288098</v>
+        <v>-3.976852634185025</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.089473655707309</v>
+        <v>1.160670566148538</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4971328596853332</v>
+        <v>-0.5098436404274426</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.453488328325096</v>
+        <v>2.44586185987983</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675894</v>
+        <v>3.746038950675896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.979370650495629</v>
+        <v>-3.801378374392556</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.164230591616084</v>
+        <v>1.235427502057313</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4971328596853332</v>
+        <v>-0.5098436404274426</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.458055560316883</v>
+        <v>2.450429091871618</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502074769544</v>
+        <v>3.765020747695441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.756346750014881</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.090306903136877</v>
+        <v>-3.912314627033805</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.119867564446382</v>
+        <v>1.191064474887611</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4971328596853332</v>
+        <v>-0.5098436404274426</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.458067034203681</v>
+        <v>2.450440565758415</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581285</v>
+        <v>3.773206721581287</v>
       </c>
       <c r="C1941" t="n">
         <v>2.759478135234786</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.29333348068011</v>
+        <v>-4.115341204577038</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.041788318648995</v>
+        <v>1.112985229090224</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.7001594372285667</v>
+        <v>-0.712870217970676</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.339382472897646</v>
+        <v>2.331756004452381</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734155</v>
+        <v>3.784340376734156</v>
       </c>
       <c r="C1942" t="n">
         <v>2.769650521666918</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.135407881744817</v>
+        <v>-3.957415605641745</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.115130944655244</v>
+        <v>1.186327855096473</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.7001594372285667</v>
+        <v>-0.712870217970676</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.349554859329779</v>
+        <v>2.341928390884513</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.764596792240779</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.283729135555946</v>
+        <v>-4.105736859452874</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.050748713704653</v>
+        <v>1.121945624145882</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.7001594372285667</v>
+        <v>-0.712870217970676</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.344501129903639</v>
+        <v>2.336874661458373</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.562266635862971</v>
+        <v>3.770328893719144</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.666636672186587</v>
+        <v>2.756372567685304</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.283729135555946</v>
+        <v>-4.22097171919228</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.050748713704653</v>
+        <v>1.067627455694645</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.7001594372285667</v>
+        <v>-0.8281050777100817</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.659700469172955</v>
+        <v>2.259509521059256</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240424.xlsx
+++ b/tame_output/ON/bt/strategyON_20240424.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,27 +849,27 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-36.0%</t>
+          <t>-24.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.4%</t>
+          <t>-79.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.2%</t>
+          <t>116.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.6%</t>
+          <t>135.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.3%</t>
+          <t>95.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-75.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-280.6%</t>
+          <t>-277.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-583.7%</t>
+          <t>-573.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-31.7%</t>
+          <t>-36.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-269.5%</t>
+          <t>-254.1%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-36.3%</t>
+          <t>-35.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-30.3%</t>
+          <t>-29.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-167.5%</t>
+          <t>-167.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-306.8%</t>
+          <t>-296.7%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-220.1%</t>
+          <t>-202.7%</t>
         </is>
       </c>
     </row>
@@ -43658,7 +43658,7 @@
         <v>45293</v>
       </c>
       <c r="B1831" t="n">
-        <v>3.346417924612275</v>
+        <v>3.346417924612276</v>
       </c>
       <c r="C1831" t="n">
         <v>3.12760327346781</v>
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705545</v>
+        <v>3.311607601705546</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045693</v>
+        <v>3.317575502045694</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43750,7 +43750,7 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831153</v>
+        <v>3.320996253831155</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355689</v>
+        <v>3.311888301355691</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279813</v>
+        <v>3.385382209279816</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511404</v>
+        <v>3.367379938511407</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386094</v>
+        <v>3.376932391386096</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998562</v>
+        <v>3.367370539998564</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082126</v>
+        <v>3.299560092082128</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757924</v>
+        <v>3.293490533757926</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760742</v>
+        <v>3.293766719760744</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706672</v>
+        <v>3.298730590706674</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296839</v>
+        <v>3.299918119296841</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.29550733020149</v>
+        <v>3.295507330201492</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153009</v>
+        <v>3.258791981153011</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537428</v>
+        <v>3.27116857953743</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.272760131382195</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074625</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213495</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.278199702495501</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347057</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130019</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178246</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.305316798207814</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310983</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006534</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330521</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191736</v>
+        <v>3.302618194191739</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097823</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969593</v>
+        <v>3.424633354969597</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.41997943392309</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.50351550673717</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776676</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407492</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234394</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767397</v>
+        <v>3.4920980657674</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628919</v>
+        <v>3.600034689628922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085277</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702408</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781945</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567241</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78930753648777</v>
+        <v>3.789307536487774</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309722</v>
+        <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858725</v>
+        <v>3.83937087185873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85615817609647</v>
+        <v>3.856158176096476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761805</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860424</v>
+        <v>3.763178672860428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430985</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077641</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457899</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.165962807196046</v>
+        <v>-8.238812378204072</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.3107116976702886</v>
+        <v>-0.3398515260734993</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.321890310885344</v>
+        <v>-2.39473988189337</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.562895662990671</v>
+        <v>1.519185920385855</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568105</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.122414400425354</v>
+        <v>-8.195263971433381</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3002529470571051</v>
+        <v>-0.3293927754603159</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.321890310885344</v>
+        <v>-2.39473988189337</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.555935050895578</v>
+        <v>1.512225308290762</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963416</v>
+        <v>3.782918957963419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.880266006971496</v>
+        <v>-7.953115577979522</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1889312352944188</v>
+        <v>-0.2180710636976295</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.321890310885344</v>
+        <v>-2.39473988189337</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.570397405276721</v>
+        <v>1.526687662671905</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192814</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.817036635203148</v>
+        <v>-7.889886206211174</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1691073661278848</v>
+        <v>-0.1982471945310951</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.321890310885344</v>
+        <v>-2.39473988189337</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.564929525735916</v>
+        <v>1.5212197831311</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262044</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.630548942826142</v>
+        <v>-7.703398513834168</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.09701419516650533</v>
+        <v>-0.1261540235697161</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.135402618508337</v>
+        <v>-2.208252189516364</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.674320235172696</v>
+        <v>1.630610492567881</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389906</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.609399743922698</v>
+        <v>-7.682249314930725</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.08085353736780299</v>
+        <v>-0.1099933657710133</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.114253419604894</v>
+        <v>-2.18710299061292</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.694710732752088</v>
+        <v>1.651000990147272</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788091</v>
+        <v>3.748324832788095</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.365634301939254</v>
+        <v>-7.43848387294728</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.0124333477726255</v>
+        <v>-0.01670648063058477</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.114253419604894</v>
+        <v>-2.18710299061292</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.690491441099139</v>
+        <v>1.646781698494323</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527523</v>
+        <v>3.824307657527526</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.101606234745994</v>
+        <v>-7.17445580575402</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1201688885699457</v>
+        <v>0.0910290601667354</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.912388020788941</v>
+        <v>-1.985237591796967</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.813734994308727</v>
+        <v>1.770025251703911</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635139874918</v>
+        <v>3.826351398749183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.851755840796919</v>
+        <v>-6.924605411804945</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2128511211332778</v>
+        <v>0.183711292730067</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.912388020788941</v>
+        <v>-1.985237591796967</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.806477069292429</v>
+        <v>1.762767326687613</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481493</v>
+        <v>3.835954411481496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.54818835179294</v>
+        <v>-6.621037922800967</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3378772402555179</v>
+        <v>0.3087374118523076</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.912388020788941</v>
+        <v>-1.985237591796967</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.810076192813078</v>
+        <v>1.766366450208262</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862982</v>
+        <v>3.780930335862985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.474708442940926</v>
+        <v>-6.547558013948953</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3805967098508773</v>
+        <v>0.3514568814476666</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.838908111936926</v>
+        <v>-1.911757682944953</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.86749164417884</v>
+        <v>1.823781901574024</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102777</v>
+        <v>3.773761647102781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.249675443272103</v>
+        <v>-6.32252501428013</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4696303873347034</v>
+        <v>0.4404905589314927</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.613875112268103</v>
+        <v>-1.68672468327613</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.00153192159643</v>
+        <v>1.957822178991615</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353069</v>
+        <v>3.764614304353073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.035041065635697</v>
+        <v>-6.107890636643723</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5601789394435834</v>
+        <v>0.5310391110403727</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.399240734631697</v>
+        <v>-1.472090305639723</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.135007349232592</v>
+        <v>2.091297606627776</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544777</v>
+        <v>3.798811195544782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.768440708661345</v>
+        <v>-5.841290279669371</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.64801334101712</v>
+        <v>0.6188735126139093</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.399240734631697</v>
+        <v>-1.472090305639723</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.116201608016387</v>
+        <v>2.072491865411572</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769130871229</v>
+        <v>3.797691308712293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.528010211856484</v>
+        <v>-5.600859782864511</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7459286163639414</v>
+        <v>0.7167887879607306</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.158810237826836</v>
+        <v>-1.231659808834863</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.262202982724181</v>
+        <v>2.218493240119365</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82158993383768</v>
+        <v>3.821589933837684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.285219404207039</v>
+        <v>-5.358068975215065</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8469742532585398</v>
+        <v>0.8178344248553291</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.158810237826836</v>
+        <v>-1.231659808834863</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.266132296559001</v>
+        <v>2.222422553954186</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349962</v>
+        <v>3.822323422349966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.169279554581854</v>
+        <v>-5.24212912558988</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8940287770259538</v>
+        <v>0.8648889486227431</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.081988506810712</v>
+        <v>-1.154838077818739</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.312903919086016</v>
+        <v>2.2691941764812</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972335</v>
+        <v>3.84861305097234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.92662396615869</v>
+        <v>-4.999473537166716</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9880890836152127</v>
+        <v>0.9589492552120022</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.081988506810712</v>
+        <v>-1.154838077818739</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.309901990306009</v>
+        <v>2.266192247701193</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145934</v>
+        <v>3.818665376145939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.70660316812168</v>
+        <v>-4.779452739129706</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.077676439840631</v>
+        <v>1.048536611437421</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.9407686617427322</v>
+        <v>-1.013618232750759</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.396212934357411</v>
+        <v>2.352503191752596</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009946</v>
+        <v>3.84327095200995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.50735453821687</v>
+        <v>-4.580204109224897</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.173270074604378</v>
+        <v>1.144130246201168</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.9407686617427322</v>
+        <v>-1.013618232750759</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.412107117159235</v>
+        <v>2.368397374554418</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966255</v>
+        <v>3.845043810966258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.347839434697501</v>
+        <v>-4.420689005705527</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.238221960452428</v>
+        <v>1.209082132049217</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.7812535582233623</v>
+        <v>-0.8541031292313886</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.508962023711158</v>
+        <v>2.465252281106343</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046991</v>
+        <v>3.791269976046996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.203167289597763</v>
+        <v>-4.27601686060579</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.306178921053763</v>
+        <v>1.277039092650552</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.6365814131236249</v>
+        <v>-0.7094309841316513</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.60585341333244</v>
+        <v>2.562143670727625</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412098</v>
+        <v>3.735835647412103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.185397830666807</v>
+        <v>-4.258247401674834</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.228626396712867</v>
+        <v>1.199486568309656</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.6188119541926693</v>
+        <v>-0.6916615252006957</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.531854780777735</v>
+        <v>2.48814503817292</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144511</v>
+        <v>3.762643902144516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.098598332887798</v>
+        <v>-4.171447903895825</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.285746689147036</v>
+        <v>1.256606860743826</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.6188119541926693</v>
+        <v>-0.6916615252006957</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.554255274100302</v>
+        <v>2.510545531495486</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900689</v>
+        <v>3.729142822900694</v>
       </c>
       <c r="C1935" t="n">
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.998905718158786</v>
+        <v>-4.071755289166813</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.325696136412053</v>
+        <v>1.296556308008843</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.5191193394636575</v>
+        <v>-0.5919689104716839</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.614143244311121</v>
+        <v>2.570433501706305</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473595</v>
+        <v>3.7432166204736</v>
       </c>
       <c r="C1936" t="n">
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.067275904482797</v>
+        <v>-4.140125475490823</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.309354984357151</v>
+        <v>1.280215155953941</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.5098436404274426</v>
+        <v>-0.5826932114354689</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.630715586207552</v>
+        <v>2.587005843602736</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978364</v>
+        <v>3.71417556397837</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.94585947485632</v>
+        <v>-4.018709045864346</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.348358264839633</v>
+        <v>1.319218436436423</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.5098436404274426</v>
+        <v>-0.5826932114354689</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.621152294839443</v>
+        <v>2.577442552234627</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887697</v>
+        <v>3.710903155887703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.976852634185025</v>
+        <v>-4.049702205193052</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.160670566148538</v>
+        <v>1.131530737745327</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.5098436404274426</v>
+        <v>-0.5826932114354689</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.44586185987983</v>
+        <v>2.402152117275014</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675896</v>
+        <v>3.7460389506759</v>
       </c>
       <c r="C1939" t="n">
         <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.801378374392556</v>
+        <v>-3.874227945400583</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.235427502057313</v>
+        <v>1.206287673654103</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.5098436404274426</v>
+        <v>-0.5826932114354689</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.450429091871618</v>
+        <v>2.406719349266802</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695441</v>
+        <v>3.765020747695445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.756346750014881</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.912314627033805</v>
+        <v>-3.985164198041831</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.191064474887611</v>
+        <v>1.161924646484401</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.5098436404274426</v>
+        <v>-0.5826932114354689</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.450440565758415</v>
+        <v>2.4067308231536</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581287</v>
+        <v>3.77320672158129</v>
       </c>
       <c r="C1941" t="n">
         <v>2.759478135234786</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.115341204577038</v>
+        <v>-4.188190775585064</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.112985229090224</v>
+        <v>1.083845400687013</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.712870217970676</v>
+        <v>-0.7857197889787023</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.331756004452381</v>
+        <v>2.288046261847565</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734156</v>
+        <v>3.784340376734159</v>
       </c>
       <c r="C1942" t="n">
         <v>2.769650521666918</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.957415605641745</v>
+        <v>-4.030265176649771</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.186327855096473</v>
+        <v>1.157188026693263</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.712870217970676</v>
+        <v>-0.7857197889787023</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.341928390884513</v>
+        <v>2.298218648279697</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212292</v>
+        <v>3.786946382212295</v>
       </c>
       <c r="C1943" t="n">
         <v>2.764596792240779</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.105736859452874</v>
+        <v>-4.1785864304609</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.121945624145882</v>
+        <v>1.092805795742672</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.712870217970676</v>
+        <v>-0.7857197889787023</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.336874661458373</v>
+        <v>2.293164918853558</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.770328893719144</v>
+        <v>3.461742435667624</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.756372567685304</v>
+        <v>2.869028787213317</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.22097171919228</v>
+        <v>-4.119602919108418</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.067627455694645</v>
+        <v>1.220831195256202</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.8281050777100817</v>
+        <v>-0.7267362776262207</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.259509521059256</v>
+        <v>2.432987020637585</v>
       </c>
     </row>
   </sheetData>
